--- a/05_Figures/HRvLR/S03_Signatures/c_data/s03_signatures.xlsx
+++ b/05_Figures/HRvLR/S03_Signatures/c_data/s03_signatures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="214">
   <si>
     <t>sheet</t>
   </si>
@@ -232,16 +232,16 @@
     <t>contrasts</t>
   </si>
   <si>
-    <t>02_HRvLR_groups/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
-  </si>
-  <si>
-    <t>0d6cf853ff8d0d35c8767a6734aeecb9</t>
+    <t>03_Group_comparisons/HRvLR/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
+  </si>
+  <si>
+    <t>4a09b3edb7bc9a8d0cee075927563827</t>
   </si>
   <si>
     <t>set_tests</t>
   </si>
   <si>
-    <t>02_HRvLR_groups/03_Set_Contrasts/c_data/set_tests.rds</t>
+    <t>03_Group_comparisons/HRvLR/03_Set_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
     <t>b928dfb75f0631b92e8ffaf819778f86</t>
@@ -349,12 +349,24 @@
     <t>1.2.1</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
     <t>foreach</t>
   </si>
   <si>
@@ -412,6 +424,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -424,6 +448,18 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -433,9 +469,6 @@
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>limma</t>
   </si>
   <si>
@@ -454,6 +487,12 @@
     <t>1.5.0</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
+  </si>
+  <si>
     <t>patchwork</t>
   </si>
   <si>
@@ -529,6 +568,12 @@
     <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -605,6 +650,18 @@
   </si>
   <si>
     <t>3.0.2</t>
+  </si>
+  <si>
+    <t>xfun</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -2485,7 +2542,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -2746,7 +2803,7 @@
         <v>121</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
         <v>80</v>
@@ -2754,10 +2811,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
         <v>80</v>
@@ -2765,10 +2822,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
         <v>80</v>
@@ -2804,7 +2861,7 @@
         <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2900,7 +2957,7 @@
         <v>148</v>
       </c>
       <c r="B38" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s">
         <v>80</v>
@@ -2908,21 +2965,21 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>149</v>
+      </c>
+      <c r="B39" t="s">
         <v>150</v>
       </c>
-      <c r="B39" t="s">
-        <v>151</v>
-      </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>151</v>
+      </c>
+      <c r="B40" t="s">
         <v>152</v>
-      </c>
-      <c r="B40" t="s">
-        <v>153</v>
       </c>
       <c r="C40" t="s">
         <v>80</v>
@@ -2930,10 +2987,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" t="s">
         <v>154</v>
-      </c>
-      <c r="B41" t="s">
-        <v>155</v>
       </c>
       <c r="C41" t="s">
         <v>80</v>
@@ -2941,10 +2998,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>155</v>
+      </c>
+      <c r="B42" t="s">
         <v>156</v>
-      </c>
-      <c r="B42" t="s">
-        <v>157</v>
       </c>
       <c r="C42" t="s">
         <v>80</v>
@@ -2952,10 +3009,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>157</v>
+      </c>
+      <c r="B43" t="s">
         <v>158</v>
-      </c>
-      <c r="B43" t="s">
-        <v>159</v>
       </c>
       <c r="C43" t="s">
         <v>80</v>
@@ -2963,10 +3020,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
+        <v>159</v>
+      </c>
+      <c r="B44" t="s">
         <v>160</v>
-      </c>
-      <c r="B44" t="s">
-        <v>161</v>
       </c>
       <c r="C44" t="s">
         <v>80</v>
@@ -2974,10 +3031,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
+        <v>161</v>
+      </c>
+      <c r="B45" t="s">
         <v>162</v>
-      </c>
-      <c r="B45" t="s">
-        <v>163</v>
       </c>
       <c r="C45" t="s">
         <v>80</v>
@@ -2985,10 +3042,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
+        <v>163</v>
+      </c>
+      <c r="B46" t="s">
         <v>164</v>
-      </c>
-      <c r="B46" t="s">
-        <v>165</v>
       </c>
       <c r="C46" t="s">
         <v>80</v>
@@ -2996,21 +3053,21 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
+        <v>165</v>
+      </c>
+      <c r="B47" t="s">
         <v>166</v>
       </c>
-      <c r="B47" t="s">
-        <v>167</v>
-      </c>
       <c r="C47" t="s">
-        <v>168</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C48" t="s">
         <v>80</v>
@@ -3018,21 +3075,21 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C49" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B50" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C50" t="s">
         <v>80</v>
@@ -3040,10 +3097,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B51" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C51" t="s">
         <v>80</v>
@@ -3051,10 +3108,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B52" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C52" t="s">
         <v>80</v>
@@ -3062,10 +3119,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B53" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C53" t="s">
         <v>80</v>
@@ -3073,21 +3130,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
+        <v>179</v>
+      </c>
+      <c r="B54" t="s">
+        <v>180</v>
+      </c>
+      <c r="C54" t="s">
         <v>181</v>
-      </c>
-      <c r="B54" t="s">
-        <v>182</v>
-      </c>
-      <c r="C54" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
+        <v>182</v>
+      </c>
+      <c r="B55" t="s">
         <v>183</v>
-      </c>
-      <c r="B55" t="s">
-        <v>184</v>
       </c>
       <c r="C55" t="s">
         <v>80</v>
@@ -3095,10 +3152,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
+        <v>184</v>
+      </c>
+      <c r="B56" t="s">
         <v>185</v>
-      </c>
-      <c r="B56" t="s">
-        <v>145</v>
       </c>
       <c r="C56" t="s">
         <v>80</v>
@@ -3109,18 +3166,18 @@
         <v>186</v>
       </c>
       <c r="B57" t="s">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="C57" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C58" t="s">
         <v>80</v>
@@ -3128,10 +3185,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B59" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C59" t="s">
         <v>80</v>
@@ -3139,10 +3196,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B60" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C60" t="s">
         <v>80</v>
@@ -3150,12 +3207,122 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B61" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C61" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>196</v>
+      </c>
+      <c r="B62" t="s">
+        <v>197</v>
+      </c>
+      <c r="C62" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>198</v>
+      </c>
+      <c r="B63" t="s">
+        <v>199</v>
+      </c>
+      <c r="C63" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>200</v>
+      </c>
+      <c r="B64" t="s">
+        <v>158</v>
+      </c>
+      <c r="C64" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>201</v>
+      </c>
+      <c r="B65" t="s">
+        <v>108</v>
+      </c>
+      <c r="C65" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>202</v>
+      </c>
+      <c r="B66" t="s">
+        <v>203</v>
+      </c>
+      <c r="C66" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>204</v>
+      </c>
+      <c r="B67" t="s">
+        <v>205</v>
+      </c>
+      <c r="C67" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>206</v>
+      </c>
+      <c r="B68" t="s">
+        <v>207</v>
+      </c>
+      <c r="C68" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>208</v>
+      </c>
+      <c r="B69" t="s">
+        <v>209</v>
+      </c>
+      <c r="C69" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>210</v>
+      </c>
+      <c r="B70" t="s">
+        <v>211</v>
+      </c>
+      <c r="C70" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>212</v>
+      </c>
+      <c r="B71" t="s">
+        <v>213</v>
+      </c>
+      <c r="C71" t="s">
         <v>80</v>
       </c>
     </row>

--- a/05_Figures/HRvLR/S03_Signatures/c_data/s03_signatures.xlsx
+++ b/05_Figures/HRvLR/S03_Signatures/c_data/s03_signatures.xlsx
@@ -235,7 +235,7 @@
     <t>03_Group_comparisons/HRvLR/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>4a09b3edb7bc9a8d0cee075927563827</t>
+    <t>6bb93683143c481fb5481529db64870c</t>
   </si>
   <si>
     <t>set_tests</t>

--- a/05_Figures/HRvLR/S03_Signatures/c_data/s03_signatures.xlsx
+++ b/05_Figures/HRvLR/S03_Signatures/c_data/s03_signatures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="197">
   <si>
     <t>sheet</t>
   </si>
@@ -232,16 +232,16 @@
     <t>contrasts</t>
   </si>
   <si>
-    <t>03_Group_comparisons/HRvLR/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
-  </si>
-  <si>
-    <t>6bb93683143c481fb5481529db64870c</t>
+    <t>03_Group_comparisons/HRvLR/c_data/02_protein_contrasts.xlsx</t>
+  </si>
+  <si>
+    <t>c128a1560d3239cecce9981259007118</t>
   </si>
   <si>
     <t>set_tests</t>
   </si>
   <si>
-    <t>03_Group_comparisons/HRvLR/03_Set_Contrasts/c_data/set_tests.rds</t>
+    <t>03_Group_comparisons/HRvLR/c_data/03_set_tests.rds</t>
   </si>
   <si>
     <t>b928dfb75f0631b92e8ffaf819778f86</t>
@@ -349,126 +349,93 @@
     <t>1.2.1</t>
   </si>
   <si>
-    <t>evaluate</t>
+    <t>farver</t>
+  </si>
+  <si>
+    <t>2.1.2</t>
+  </si>
+  <si>
+    <t>foreach</t>
+  </si>
+  <si>
+    <t>1.5.2</t>
+  </si>
+  <si>
+    <t>generics</t>
+  </si>
+  <si>
+    <t>0.1.4</t>
+  </si>
+  <si>
+    <t>GetoptLong</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
+    <t>ggh4x</t>
+  </si>
+  <si>
+    <t>0.3.1</t>
+  </si>
+  <si>
+    <t>ggplot2</t>
+  </si>
+  <si>
+    <t>4.0.3</t>
+  </si>
+  <si>
+    <t>GlobalOptions</t>
+  </si>
+  <si>
+    <t>glue</t>
+  </si>
+  <si>
+    <t>1.8.1</t>
+  </si>
+  <si>
+    <t>gtable</t>
+  </si>
+  <si>
+    <t>0.3.6</t>
+  </si>
+  <si>
+    <t>here</t>
+  </si>
+  <si>
+    <t>1.0.2</t>
+  </si>
+  <si>
+    <t>hms</t>
+  </si>
+  <si>
+    <t>1.1.4</t>
+  </si>
+  <si>
+    <t>IRanges</t>
+  </si>
+  <si>
+    <t>2.46.0</t>
+  </si>
+  <si>
+    <t>iterators</t>
+  </si>
+  <si>
+    <t>1.0.14</t>
+  </si>
+  <si>
+    <t>labeling</t>
+  </si>
+  <si>
+    <t>0.4.3</t>
+  </si>
+  <si>
+    <t>lifecycle</t>
   </si>
   <si>
     <t>1.0.5</t>
   </si>
   <si>
-    <t>farver</t>
-  </si>
-  <si>
-    <t>2.1.2</t>
-  </si>
-  <si>
-    <t>fastmap</t>
-  </si>
-  <si>
-    <t>1.2.0</t>
-  </si>
-  <si>
-    <t>foreach</t>
-  </si>
-  <si>
-    <t>1.5.2</t>
-  </si>
-  <si>
-    <t>generics</t>
-  </si>
-  <si>
-    <t>0.1.4</t>
-  </si>
-  <si>
-    <t>GetoptLong</t>
-  </si>
-  <si>
-    <t>1.1.1</t>
-  </si>
-  <si>
-    <t>ggh4x</t>
-  </si>
-  <si>
-    <t>0.3.1</t>
-  </si>
-  <si>
-    <t>ggplot2</t>
-  </si>
-  <si>
-    <t>4.0.3</t>
-  </si>
-  <si>
-    <t>GlobalOptions</t>
-  </si>
-  <si>
-    <t>glue</t>
-  </si>
-  <si>
-    <t>1.8.1</t>
-  </si>
-  <si>
-    <t>gtable</t>
-  </si>
-  <si>
-    <t>0.3.6</t>
-  </si>
-  <si>
-    <t>here</t>
-  </si>
-  <si>
-    <t>1.0.2</t>
-  </si>
-  <si>
-    <t>hms</t>
-  </si>
-  <si>
-    <t>1.1.4</t>
-  </si>
-  <si>
-    <t>htmltools</t>
-  </si>
-  <si>
-    <t>0.5.9</t>
-  </si>
-  <si>
-    <t>htmlwidgets</t>
-  </si>
-  <si>
-    <t>1.6.4</t>
-  </si>
-  <si>
-    <t>IRanges</t>
-  </si>
-  <si>
-    <t>2.46.0</t>
-  </si>
-  <si>
-    <t>iterators</t>
-  </si>
-  <si>
-    <t>1.0.14</t>
-  </si>
-  <si>
-    <t>jsonlite</t>
-  </si>
-  <si>
-    <t>2.0.0</t>
-  </si>
-  <si>
-    <t>knitr</t>
-  </si>
-  <si>
-    <t>1.51</t>
-  </si>
-  <si>
-    <t>labeling</t>
-  </si>
-  <si>
-    <t>0.4.3</t>
-  </si>
-  <si>
-    <t>lifecycle</t>
-  </si>
-  <si>
     <t>limma</t>
   </si>
   <si>
@@ -487,12 +454,6 @@
     <t>1.5.0</t>
   </si>
   <si>
-    <t>otel</t>
-  </si>
-  <si>
-    <t>0.2.0</t>
-  </si>
-  <si>
     <t>patchwork</t>
   </si>
   <si>
@@ -568,12 +529,6 @@
     <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
-    <t>rmarkdown</t>
-  </si>
-  <si>
-    <t>2.31</t>
-  </si>
-  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -650,12 +605,6 @@
   </si>
   <si>
     <t>3.0.2</t>
-  </si>
-  <si>
-    <t>xfun</t>
-  </si>
-  <si>
-    <t>0.57</t>
   </si>
   <si>
     <t>yaml</t>
@@ -2542,7 +2491,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -2803,7 +2752,7 @@
         <v>121</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C24" t="s">
         <v>80</v>
@@ -2811,10 +2760,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" t="s">
         <v>123</v>
-      </c>
-      <c r="B25" t="s">
-        <v>124</v>
       </c>
       <c r="C25" t="s">
         <v>80</v>
@@ -2822,10 +2771,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" t="s">
         <v>125</v>
-      </c>
-      <c r="B26" t="s">
-        <v>118</v>
       </c>
       <c r="C26" t="s">
         <v>80</v>
@@ -2861,7 +2810,7 @@
         <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2957,7 +2906,7 @@
         <v>148</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="C38" t="s">
         <v>80</v>
@@ -2965,21 +2914,21 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B39" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C40" t="s">
         <v>80</v>
@@ -2987,10 +2936,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C41" t="s">
         <v>80</v>
@@ -2998,10 +2947,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C42" t="s">
         <v>80</v>
@@ -3009,10 +2958,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C43" t="s">
         <v>80</v>
@@ -3020,10 +2969,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C44" t="s">
         <v>80</v>
@@ -3031,10 +2980,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B45" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C45" t="s">
         <v>80</v>
@@ -3042,10 +2991,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C46" t="s">
         <v>80</v>
@@ -3053,21 +3002,21 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B47" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C47" t="s">
-        <v>80</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B48" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C48" t="s">
         <v>80</v>
@@ -3075,21 +3024,21 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B49" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C49" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C50" t="s">
         <v>80</v>
@@ -3097,10 +3046,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B51" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C51" t="s">
         <v>80</v>
@@ -3108,10 +3057,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C52" t="s">
         <v>80</v>
@@ -3119,10 +3068,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B53" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C53" t="s">
         <v>80</v>
@@ -3130,21 +3079,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B54" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C54" t="s">
-        <v>181</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C55" t="s">
         <v>80</v>
@@ -3152,10 +3101,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B56" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="C56" t="s">
         <v>80</v>
@@ -3166,18 +3115,18 @@
         <v>186</v>
       </c>
       <c r="B57" t="s">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="C57" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
+        <v>187</v>
+      </c>
+      <c r="B58" t="s">
         <v>188</v>
-      </c>
-      <c r="B58" t="s">
-        <v>189</v>
       </c>
       <c r="C58" t="s">
         <v>80</v>
@@ -3185,10 +3134,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
+        <v>189</v>
+      </c>
+      <c r="B59" t="s">
         <v>190</v>
-      </c>
-      <c r="B59" t="s">
-        <v>191</v>
       </c>
       <c r="C59" t="s">
         <v>80</v>
@@ -3196,10 +3145,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
+        <v>191</v>
+      </c>
+      <c r="B60" t="s">
         <v>192</v>
-      </c>
-      <c r="B60" t="s">
-        <v>193</v>
       </c>
       <c r="C60" t="s">
         <v>80</v>
@@ -3207,10 +3156,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
+        <v>193</v>
+      </c>
+      <c r="B61" t="s">
         <v>194</v>
-      </c>
-      <c r="B61" t="s">
-        <v>195</v>
       </c>
       <c r="C61" t="s">
         <v>80</v>
@@ -3218,111 +3167,12 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
+        <v>195</v>
+      </c>
+      <c r="B62" t="s">
         <v>196</v>
       </c>
-      <c r="B62" t="s">
-        <v>197</v>
-      </c>
       <c r="C62" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>198</v>
-      </c>
-      <c r="B63" t="s">
-        <v>199</v>
-      </c>
-      <c r="C63" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
-        <v>200</v>
-      </c>
-      <c r="B64" t="s">
-        <v>158</v>
-      </c>
-      <c r="C64" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>201</v>
-      </c>
-      <c r="B65" t="s">
-        <v>108</v>
-      </c>
-      <c r="C65" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>202</v>
-      </c>
-      <c r="B66" t="s">
-        <v>203</v>
-      </c>
-      <c r="C66" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
-        <v>204</v>
-      </c>
-      <c r="B67" t="s">
-        <v>205</v>
-      </c>
-      <c r="C67" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
-        <v>206</v>
-      </c>
-      <c r="B68" t="s">
-        <v>207</v>
-      </c>
-      <c r="C68" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
-        <v>208</v>
-      </c>
-      <c r="B69" t="s">
-        <v>209</v>
-      </c>
-      <c r="C69" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
-        <v>210</v>
-      </c>
-      <c r="B70" t="s">
-        <v>211</v>
-      </c>
-      <c r="C70" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" t="s">
-        <v>212</v>
-      </c>
-      <c r="B71" t="s">
-        <v>213</v>
-      </c>
-      <c r="C71" t="s">
         <v>80</v>
       </c>
     </row>

--- a/05_Figures/HRvLR/S03_Signatures/c_data/s03_signatures.xlsx
+++ b/05_Figures/HRvLR/S03_Signatures/c_data/s03_signatures.xlsx
@@ -37,13 +37,13 @@
     <t>pi_barcode</t>
   </si>
   <si>
-    <t>Panels a, b: each arm's Pi &lt; 0.05 sets in the other arm's ranking: n, % same way, fry FDR.</t>
+    <t>Panels a, b: each group's Pi &lt; 0.05 sets in the other group's ranking: n, % same way, fry FDR.</t>
   </si>
   <si>
     <t>trajectory</t>
   </si>
   <si>
-    <t>Panel c: mean change from each subject's T1 (and SE) per training set, arm and time point.</t>
+    <t>Panel c: mean change from each subject's T1 (and SE) per training set, group and time point.</t>
   </si>
   <si>
     <t>window_stats</t>
@@ -130,10 +130,10 @@
     <t>Proteins in the module or set.</t>
   </si>
   <si>
-    <t>arm</t>
-  </si>
-  <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
+    <t>group</t>
+  </si>
+  <si>
+    <t>Group the row belongs to: HR or LR, or C1 or C2 in a proteome grouping.</t>
   </si>
   <si>
     <t>timepoint</t>
@@ -235,7 +235,7 @@
     <t>03_Group_comparisons/HRvLR/c_data/02_protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>c128a1560d3239cecce9981259007118</t>
+    <t>6513b98af7f564bb10c517dbdd3ee251</t>
   </si>
   <si>
     <t>set_tests</t>
